--- a/data/trans_orig/Q17H_R-Clase-trans_orig.xlsx
+++ b/data/trans_orig/Q17H_R-Clase-trans_orig.xlsx
@@ -677,12 +677,12 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,85; 1,11</t>
+          <t>0,84; 1,12</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,89; 1,46</t>
+          <t>0,9; 1,4</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -692,12 +692,12 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,64; 0,96</t>
+          <t>0,64; 0,97</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,51; 0,71</t>
+          <t>0,51; 0,72</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -707,12 +707,12 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,8; 1,0</t>
+          <t>0,79; 1,02</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,75; 1,1</t>
+          <t>0,76; 1,11</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -787,27 +787,27 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,98; 1,48</t>
+          <t>1,01; 1,51</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,67; 0,92</t>
+          <t>0,67; 0,94</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,23; 0,3</t>
+          <t>0,24; 0,3</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,65; 0,9</t>
+          <t>0,66; 0,9</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,5; 0,87</t>
+          <t>0,5; 0,89</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,86; 1,15</t>
+          <t>0,87; 1,15</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,63; 0,86</t>
+          <t>0,64; 0,85</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -897,12 +897,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,06; 1,68</t>
+          <t>1,06; 1,64</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,93; 1,43</t>
+          <t>0,94; 1,39</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -912,27 +912,27 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,59; 1,09</t>
+          <t>0,57; 1,07</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,53; 0,8</t>
+          <t>0,52; 0,81</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,22; 0,3</t>
+          <t>0,21; 0,31</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,0; 1,5</t>
+          <t>0,98; 1,43</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,86; 1,21</t>
+          <t>0,85; 1,2</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -1022,12 +1022,12 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,63; 0,81</t>
+          <t>0,64; 0,8</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,59; 1,06</t>
+          <t>0,59; 1,04</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1117,12 +1117,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,24; 1,82</t>
+          <t>1,27; 1,88</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,79; 1,14</t>
+          <t>0,79; 1,13</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1132,12 +1132,12 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,6; 0,8</t>
+          <t>0,61; 0,81</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,47; 0,63</t>
+          <t>0,47; 0,62</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1147,12 +1147,12 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,92; 1,19</t>
+          <t>0,91; 1,22</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,63; 0,83</t>
+          <t>0,63; 0,81</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -1164,7 +1164,7 @@
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1227,12 +1227,12 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,96; 1,18</t>
+          <t>0,97; 1,2</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,82; 1,05</t>
+          <t>0,82; 1,07</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -1242,7 +1242,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,66; 0,83</t>
+          <t>0,65; 0,84</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1257,17 +1257,17 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,74; 0,9</t>
+          <t>0,74; 0,89</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,56; 0,67</t>
+          <t>0,57; 0,68</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0,22; 0,25</t>
+          <t>0,22; 0,26</t>
         </is>
       </c>
     </row>
@@ -1337,12 +1337,12 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>1,07; 1,21</t>
+          <t>1,07; 1,22</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,9; 1,04</t>
+          <t>0,9; 1,05</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -1352,7 +1352,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,69; 0,78</t>
+          <t>0,68; 0,77</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -1367,12 +1367,12 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,9; 0,99</t>
+          <t>0,89; 0,98</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,74; 0,84</t>
+          <t>0,75; 0,84</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
